--- a/artfynd/A 60213-2019 artfynd.xlsx
+++ b/artfynd/A 60213-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747285</v>
+        <v>122747286</v>
       </c>
       <c r="B2" t="n">
-        <v>90837</v>
+        <v>78146</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6437</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473856</v>
+        <v>473862</v>
       </c>
       <c r="R2" t="n">
-        <v>6863073</v>
+        <v>6863070</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747289</v>
+        <v>122747290</v>
       </c>
       <c r="B3" t="n">
-        <v>79741</v>
+        <v>90960</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,34 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Juvikberget SÖ, Hjd</t>
+          <t>Juvikberget NÖ, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473867</v>
+        <v>473862</v>
       </c>
       <c r="R3" t="n">
-        <v>6862964</v>
+        <v>6862948</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747286</v>
+        <v>122747253</v>
       </c>
       <c r="B4" t="n">
-        <v>78044</v>
+        <v>79843</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,34 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Solandsberget N, Hjd</t>
+          <t>Krankpunsen V, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473862</v>
+        <v>473668</v>
       </c>
       <c r="R4" t="n">
-        <v>6863070</v>
+        <v>6863018</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
         <v>122747288</v>
       </c>
       <c r="B5" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747290</v>
+        <v>122747291</v>
       </c>
       <c r="B6" t="n">
-        <v>90857</v>
+        <v>79843</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473862</v>
+        <v>473850</v>
       </c>
       <c r="R6" t="n">
-        <v>6862948</v>
+        <v>6862934</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747252</v>
+        <v>122747292</v>
       </c>
       <c r="B7" t="n">
-        <v>79742</v>
+        <v>79844</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,14 +1241,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Krankpunsen V, Hjd</t>
+          <t>Juvikberget NÖ, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473691</v>
+        <v>473850</v>
       </c>
       <c r="R7" t="n">
-        <v>6863000</v>
+        <v>6862934</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122747292</v>
+        <v>122747293</v>
       </c>
       <c r="B8" t="n">
-        <v>79742</v>
+        <v>79844</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,14 +1347,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Juvikberget NÖ, Hjd</t>
+          <t>Juvikberget N, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473850</v>
+        <v>473861</v>
       </c>
       <c r="R8" t="n">
-        <v>6862934</v>
+        <v>6862933</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747253</v>
+        <v>122747285</v>
       </c>
       <c r="B9" t="n">
-        <v>79741</v>
+        <v>90940</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,34 +1433,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Krankpunsen V, Hjd</t>
+          <t>Solandsberget N, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473668</v>
+        <v>473856</v>
       </c>
       <c r="R9" t="n">
-        <v>6863018</v>
+        <v>6863073</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747293</v>
+        <v>122747252</v>
       </c>
       <c r="B10" t="n">
-        <v>79742</v>
+        <v>79844</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,14 +1559,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Juvikberget N, Hjd</t>
+          <t>Krankpunsen V, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473861</v>
+        <v>473691</v>
       </c>
       <c r="R10" t="n">
-        <v>6862933</v>
+        <v>6863000</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122747291</v>
+        <v>122747289</v>
       </c>
       <c r="B11" t="n">
-        <v>79741</v>
+        <v>79843</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1665,14 +1665,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Juvikberget NÖ, Hjd</t>
+          <t>Juvikberget SÖ, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473850</v>
+        <v>473867</v>
       </c>
       <c r="R11" t="n">
-        <v>6862934</v>
+        <v>6862964</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 60213-2019 artfynd.xlsx
+++ b/artfynd/A 60213-2019 artfynd.xlsx
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747288</v>
+        <v>122747291</v>
       </c>
       <c r="B5" t="n">
-        <v>98347</v>
+        <v>79843</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,38 +1005,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Juvikberget Ö, Hjd</t>
+          <t>Juvikberget NÖ, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473875</v>
+        <v>473850</v>
       </c>
       <c r="R5" t="n">
-        <v>6863006</v>
+        <v>6862934</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747291</v>
+        <v>122747288</v>
       </c>
       <c r="B6" t="n">
-        <v>79843</v>
+        <v>98347</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,38 +1111,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Juvikberget NÖ, Hjd</t>
+          <t>Juvikberget Ö, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473850</v>
+        <v>473875</v>
       </c>
       <c r="R6" t="n">
-        <v>6862934</v>
+        <v>6863006</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 60213-2019 artfynd.xlsx
+++ b/artfynd/A 60213-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747286</v>
+        <v>122747253</v>
       </c>
       <c r="B2" t="n">
-        <v>78146</v>
+        <v>79847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6437</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Solandsberget N, Hjd</t>
+          <t>Krankpunsen V, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473862</v>
+        <v>473668</v>
       </c>
       <c r="R2" t="n">
-        <v>6863070</v>
+        <v>6863018</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747290</v>
+        <v>122747292</v>
       </c>
       <c r="B3" t="n">
-        <v>90960</v>
+        <v>79848</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473862</v>
+        <v>473850</v>
       </c>
       <c r="R3" t="n">
-        <v>6862948</v>
+        <v>6862934</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747253</v>
+        <v>122747288</v>
       </c>
       <c r="B4" t="n">
-        <v>79843</v>
+        <v>98355</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Krankpunsen V, Hjd</t>
+          <t>Juvikberget Ö, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473668</v>
+        <v>473875</v>
       </c>
       <c r="R4" t="n">
-        <v>6863018</v>
+        <v>6863006</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747291</v>
+        <v>122747289</v>
       </c>
       <c r="B5" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,14 +1029,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Juvikberget NÖ, Hjd</t>
+          <t>Juvikberget SÖ, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473850</v>
+        <v>473867</v>
       </c>
       <c r="R5" t="n">
-        <v>6862934</v>
+        <v>6862964</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747288</v>
+        <v>122747286</v>
       </c>
       <c r="B6" t="n">
-        <v>98347</v>
+        <v>78150</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,38 +1111,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Juvikberget Ö, Hjd</t>
+          <t>Solandsberget N, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473875</v>
+        <v>473862</v>
       </c>
       <c r="R6" t="n">
-        <v>6863006</v>
+        <v>6863070</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747292</v>
+        <v>122747285</v>
       </c>
       <c r="B7" t="n">
-        <v>79844</v>
+        <v>90944</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,34 +1221,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Juvikberget NÖ, Hjd</t>
+          <t>Solandsberget N, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473850</v>
+        <v>473856</v>
       </c>
       <c r="R7" t="n">
-        <v>6862934</v>
+        <v>6863073</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122747293</v>
+        <v>122747291</v>
       </c>
       <c r="B8" t="n">
-        <v>79844</v>
+        <v>79847</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,34 +1327,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Juvikberget N, Hjd</t>
+          <t>Juvikberget NÖ, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473861</v>
+        <v>473850</v>
       </c>
       <c r="R8" t="n">
-        <v>6862933</v>
+        <v>6862934</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747285</v>
+        <v>122747252</v>
       </c>
       <c r="B9" t="n">
-        <v>90940</v>
+        <v>79848</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,34 +1433,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Solandsberget N, Hjd</t>
+          <t>Krankpunsen V, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473856</v>
+        <v>473691</v>
       </c>
       <c r="R9" t="n">
-        <v>6863073</v>
+        <v>6863000</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747252</v>
+        <v>122747293</v>
       </c>
       <c r="B10" t="n">
-        <v>79844</v>
+        <v>79848</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,14 +1559,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Krankpunsen V, Hjd</t>
+          <t>Juvikberget N, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473691</v>
+        <v>473861</v>
       </c>
       <c r="R10" t="n">
-        <v>6863000</v>
+        <v>6862933</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122747289</v>
+        <v>122747290</v>
       </c>
       <c r="B11" t="n">
-        <v>79843</v>
+        <v>90964</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,34 +1645,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Juvikberget SÖ, Hjd</t>
+          <t>Juvikberget NÖ, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473867</v>
+        <v>473862</v>
       </c>
       <c r="R11" t="n">
-        <v>6862964</v>
+        <v>6862948</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 60213-2019 artfynd.xlsx
+++ b/artfynd/A 60213-2019 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747253</v>
+        <v>122747291</v>
       </c>
       <c r="B2" t="n">
         <v>79847</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Krankpunsen V, Hjd</t>
+          <t>Juvikberget NÖ, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473668</v>
+        <v>473850</v>
       </c>
       <c r="R2" t="n">
-        <v>6863018</v>
+        <v>6862934</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747292</v>
+        <v>122747253</v>
       </c>
       <c r="B3" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,34 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Juvikberget NÖ, Hjd</t>
+          <t>Krankpunsen V, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473850</v>
+        <v>473668</v>
       </c>
       <c r="R3" t="n">
-        <v>6862934</v>
+        <v>6863018</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747288</v>
+        <v>122747290</v>
       </c>
       <c r="B4" t="n">
-        <v>98355</v>
+        <v>90964</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Juvikberget Ö, Hjd</t>
+          <t>Juvikberget NÖ, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473875</v>
+        <v>473862</v>
       </c>
       <c r="R4" t="n">
-        <v>6863006</v>
+        <v>6862948</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747289</v>
+        <v>122747252</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,34 +1009,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Juvikberget SÖ, Hjd</t>
+          <t>Krankpunsen V, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473867</v>
+        <v>473691</v>
       </c>
       <c r="R5" t="n">
-        <v>6862964</v>
+        <v>6863000</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747286</v>
+        <v>122747285</v>
       </c>
       <c r="B6" t="n">
-        <v>78150</v>
+        <v>90944</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473862</v>
+        <v>473856</v>
       </c>
       <c r="R6" t="n">
-        <v>6863070</v>
+        <v>6863073</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747285</v>
+        <v>122747289</v>
       </c>
       <c r="B7" t="n">
-        <v>90944</v>
+        <v>79847</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,34 +1221,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Solandsberget N, Hjd</t>
+          <t>Juvikberget SÖ, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473856</v>
+        <v>473867</v>
       </c>
       <c r="R7" t="n">
-        <v>6863073</v>
+        <v>6862964</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122747291</v>
+        <v>122747288</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>98355</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,38 +1323,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Juvikberget NÖ, Hjd</t>
+          <t>Juvikberget Ö, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473850</v>
+        <v>473875</v>
       </c>
       <c r="R8" t="n">
-        <v>6862934</v>
+        <v>6863006</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747252</v>
+        <v>122747293</v>
       </c>
       <c r="B9" t="n">
         <v>79848</v>
@@ -1453,14 +1453,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Krankpunsen V, Hjd</t>
+          <t>Juvikberget N, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473691</v>
+        <v>473861</v>
       </c>
       <c r="R9" t="n">
-        <v>6863000</v>
+        <v>6862933</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747293</v>
+        <v>122747286</v>
       </c>
       <c r="B10" t="n">
-        <v>79848</v>
+        <v>78150</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,34 +1539,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6437</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Juvikberget N, Hjd</t>
+          <t>Solandsberget N, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473861</v>
+        <v>473862</v>
       </c>
       <c r="R10" t="n">
-        <v>6862933</v>
+        <v>6863070</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122747290</v>
+        <v>122747292</v>
       </c>
       <c r="B11" t="n">
-        <v>90964</v>
+        <v>79848</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473862</v>
+        <v>473850</v>
       </c>
       <c r="R11" t="n">
-        <v>6862948</v>
+        <v>6862934</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 60213-2019 artfynd.xlsx
+++ b/artfynd/A 60213-2019 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747253</v>
+        <v>122747252</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473668</v>
+        <v>473691</v>
       </c>
       <c r="R3" t="n">
-        <v>6863018</v>
+        <v>6863000</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747252</v>
+        <v>122747288</v>
       </c>
       <c r="B5" t="n">
-        <v>79848</v>
+        <v>98357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,38 +1005,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Krankpunsen V, Hjd</t>
+          <t>Juvikberget Ö, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473691</v>
+        <v>473875</v>
       </c>
       <c r="R5" t="n">
-        <v>6863000</v>
+        <v>6863006</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747285</v>
+        <v>122747292</v>
       </c>
       <c r="B6" t="n">
-        <v>90944</v>
+        <v>79848</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,34 +1115,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Solandsberget N, Hjd</t>
+          <t>Juvikberget NÖ, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473856</v>
+        <v>473850</v>
       </c>
       <c r="R6" t="n">
-        <v>6863073</v>
+        <v>6862934</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747289</v>
+        <v>122747293</v>
       </c>
       <c r="B7" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,34 +1221,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Juvikberget SÖ, Hjd</t>
+          <t>Juvikberget N, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473867</v>
+        <v>473861</v>
       </c>
       <c r="R7" t="n">
-        <v>6862964</v>
+        <v>6862933</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122747288</v>
+        <v>122747253</v>
       </c>
       <c r="B8" t="n">
-        <v>98355</v>
+        <v>79847</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,38 +1323,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Juvikberget Ö, Hjd</t>
+          <t>Krankpunsen V, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473875</v>
+        <v>473668</v>
       </c>
       <c r="R8" t="n">
-        <v>6863006</v>
+        <v>6863018</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747293</v>
+        <v>122747285</v>
       </c>
       <c r="B9" t="n">
-        <v>79848</v>
+        <v>90944</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,34 +1433,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Juvikberget N, Hjd</t>
+          <t>Solandsberget N, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473861</v>
+        <v>473856</v>
       </c>
       <c r="R9" t="n">
-        <v>6862933</v>
+        <v>6863073</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122747292</v>
+        <v>122747289</v>
       </c>
       <c r="B11" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,34 +1645,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Juvikberget NÖ, Hjd</t>
+          <t>Juvikberget SÖ, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473850</v>
+        <v>473867</v>
       </c>
       <c r="R11" t="n">
-        <v>6862934</v>
+        <v>6862964</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 60213-2019 artfynd.xlsx
+++ b/artfynd/A 60213-2019 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747252</v>
+        <v>122747290</v>
       </c>
       <c r="B3" t="n">
-        <v>79848</v>
+        <v>90964</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,34 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Krankpunsen V, Hjd</t>
+          <t>Juvikberget NÖ, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473691</v>
+        <v>473862</v>
       </c>
       <c r="R3" t="n">
-        <v>6863000</v>
+        <v>6862948</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747290</v>
+        <v>122747252</v>
       </c>
       <c r="B4" t="n">
-        <v>90964</v>
+        <v>79848</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,34 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Juvikberget NÖ, Hjd</t>
+          <t>Krankpunsen V, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473862</v>
+        <v>473691</v>
       </c>
       <c r="R4" t="n">
-        <v>6862948</v>
+        <v>6863000</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 60213-2019 artfynd.xlsx
+++ b/artfynd/A 60213-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747291</v>
+        <v>122747290</v>
       </c>
       <c r="B2" t="n">
-        <v>79847</v>
+        <v>90964</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473850</v>
+        <v>473862</v>
       </c>
       <c r="R2" t="n">
-        <v>6862934</v>
+        <v>6862948</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747290</v>
+        <v>122747253</v>
       </c>
       <c r="B3" t="n">
-        <v>90964</v>
+        <v>79847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,34 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Juvikberget NÖ, Hjd</t>
+          <t>Krankpunsen V, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473862</v>
+        <v>473668</v>
       </c>
       <c r="R3" t="n">
-        <v>6862948</v>
+        <v>6863018</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747288</v>
+        <v>122747289</v>
       </c>
       <c r="B5" t="n">
-        <v>98357</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,38 +1005,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Juvikberget Ö, Hjd</t>
+          <t>Juvikberget SÖ, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473875</v>
+        <v>473867</v>
       </c>
       <c r="R5" t="n">
-        <v>6863006</v>
+        <v>6862964</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747292</v>
+        <v>122747285</v>
       </c>
       <c r="B6" t="n">
-        <v>79848</v>
+        <v>90944</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,34 +1115,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Juvikberget NÖ, Hjd</t>
+          <t>Solandsberget N, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473850</v>
+        <v>473856</v>
       </c>
       <c r="R6" t="n">
-        <v>6862934</v>
+        <v>6863073</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122747253</v>
+        <v>122747288</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>98357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,38 +1323,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Krankpunsen V, Hjd</t>
+          <t>Juvikberget Ö, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473668</v>
+        <v>473875</v>
       </c>
       <c r="R8" t="n">
-        <v>6863018</v>
+        <v>6863006</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747285</v>
+        <v>122747291</v>
       </c>
       <c r="B9" t="n">
-        <v>90944</v>
+        <v>79847</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,34 +1433,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Solandsberget N, Hjd</t>
+          <t>Juvikberget NÖ, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473856</v>
+        <v>473850</v>
       </c>
       <c r="R9" t="n">
-        <v>6863073</v>
+        <v>6862934</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747286</v>
+        <v>122747292</v>
       </c>
       <c r="B10" t="n">
-        <v>78150</v>
+        <v>79848</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,34 +1539,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6437</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Solandsberget N, Hjd</t>
+          <t>Juvikberget NÖ, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473862</v>
+        <v>473850</v>
       </c>
       <c r="R10" t="n">
-        <v>6863070</v>
+        <v>6862934</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122747289</v>
+        <v>122747286</v>
       </c>
       <c r="B11" t="n">
-        <v>79847</v>
+        <v>78150</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,34 +1645,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6437</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Juvikberget SÖ, Hjd</t>
+          <t>Solandsberget N, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473867</v>
+        <v>473862</v>
       </c>
       <c r="R11" t="n">
-        <v>6862964</v>
+        <v>6863070</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 60213-2019 artfynd.xlsx
+++ b/artfynd/A 60213-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122747290</v>
       </c>
       <c r="B2" t="n">
-        <v>90964</v>
+        <v>90972</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747253</v>
+        <v>122747291</v>
       </c>
       <c r="B3" t="n">
         <v>79847</v>
@@ -817,14 +817,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Krankpunsen V, Hjd</t>
+          <t>Juvikberget NÖ, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473668</v>
+        <v>473850</v>
       </c>
       <c r="R3" t="n">
-        <v>6863018</v>
+        <v>6862934</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747252</v>
+        <v>122747285</v>
       </c>
       <c r="B4" t="n">
-        <v>79848</v>
+        <v>90952</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,34 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Krankpunsen V, Hjd</t>
+          <t>Solandsberget N, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473691</v>
+        <v>473856</v>
       </c>
       <c r="R4" t="n">
-        <v>6863000</v>
+        <v>6863073</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747289</v>
+        <v>122747286</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>78150</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,34 +1009,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Juvikberget SÖ, Hjd</t>
+          <t>Solandsberget N, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473867</v>
+        <v>473862</v>
       </c>
       <c r="R5" t="n">
-        <v>6862964</v>
+        <v>6863070</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747285</v>
+        <v>122747293</v>
       </c>
       <c r="B6" t="n">
-        <v>90944</v>
+        <v>79848</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,34 +1115,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Solandsberget N, Hjd</t>
+          <t>Juvikberget N, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473856</v>
+        <v>473861</v>
       </c>
       <c r="R6" t="n">
-        <v>6863073</v>
+        <v>6862933</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747293</v>
+        <v>122747252</v>
       </c>
       <c r="B7" t="n">
         <v>79848</v>
@@ -1241,14 +1241,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Juvikberget N, Hjd</t>
+          <t>Krankpunsen V, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473861</v>
+        <v>473691</v>
       </c>
       <c r="R7" t="n">
-        <v>6862933</v>
+        <v>6863000</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122747288</v>
+        <v>122747253</v>
       </c>
       <c r="B8" t="n">
-        <v>98357</v>
+        <v>79847</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,38 +1323,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Juvikberget Ö, Hjd</t>
+          <t>Krankpunsen V, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473875</v>
+        <v>473668</v>
       </c>
       <c r="R8" t="n">
-        <v>6863006</v>
+        <v>6863018</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747291</v>
+        <v>122747289</v>
       </c>
       <c r="B9" t="n">
         <v>79847</v>
@@ -1453,14 +1453,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Juvikberget NÖ, Hjd</t>
+          <t>Juvikberget SÖ, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473850</v>
+        <v>473867</v>
       </c>
       <c r="R9" t="n">
-        <v>6862934</v>
+        <v>6862964</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122747286</v>
+        <v>122747288</v>
       </c>
       <c r="B11" t="n">
-        <v>78150</v>
+        <v>98365</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,38 +1641,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Solandsberget N, Hjd</t>
+          <t>Juvikberget Ö, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473862</v>
+        <v>473875</v>
       </c>
       <c r="R11" t="n">
-        <v>6863070</v>
+        <v>6863006</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 60213-2019 artfynd.xlsx
+++ b/artfynd/A 60213-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747290</v>
+        <v>122747288</v>
       </c>
       <c r="B2" t="n">
-        <v>90972</v>
+        <v>98365</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Juvikberget NÖ, Hjd</t>
+          <t>Juvikberget Ö, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473862</v>
+        <v>473875</v>
       </c>
       <c r="R2" t="n">
-        <v>6862948</v>
+        <v>6863006</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747291</v>
+        <v>122747285</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>90952</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,34 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Juvikberget NÖ, Hjd</t>
+          <t>Solandsberget N, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473850</v>
+        <v>473856</v>
       </c>
       <c r="R3" t="n">
-        <v>6862934</v>
+        <v>6863073</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747285</v>
+        <v>122747291</v>
       </c>
       <c r="B4" t="n">
-        <v>90952</v>
+        <v>79847</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,34 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Solandsberget N, Hjd</t>
+          <t>Juvikberget NÖ, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473856</v>
+        <v>473850</v>
       </c>
       <c r="R4" t="n">
-        <v>6863073</v>
+        <v>6862934</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747286</v>
+        <v>122747293</v>
       </c>
       <c r="B5" t="n">
-        <v>78150</v>
+        <v>79848</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,34 +1009,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Solandsberget N, Hjd</t>
+          <t>Juvikberget N, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473862</v>
+        <v>473861</v>
       </c>
       <c r="R5" t="n">
-        <v>6863070</v>
+        <v>6862933</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747293</v>
+        <v>122747252</v>
       </c>
       <c r="B6" t="n">
         <v>79848</v>
@@ -1135,14 +1135,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Juvikberget N, Hjd</t>
+          <t>Krankpunsen V, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473861</v>
+        <v>473691</v>
       </c>
       <c r="R6" t="n">
-        <v>6862933</v>
+        <v>6863000</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747252</v>
+        <v>122747290</v>
       </c>
       <c r="B7" t="n">
-        <v>79848</v>
+        <v>90972</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,34 +1221,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Krankpunsen V, Hjd</t>
+          <t>Juvikberget NÖ, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473691</v>
+        <v>473862</v>
       </c>
       <c r="R7" t="n">
-        <v>6863000</v>
+        <v>6862948</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747289</v>
+        <v>122747286</v>
       </c>
       <c r="B9" t="n">
-        <v>79847</v>
+        <v>78150</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,34 +1433,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6437</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Juvikberget SÖ, Hjd</t>
+          <t>Solandsberget N, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473867</v>
+        <v>473862</v>
       </c>
       <c r="R9" t="n">
-        <v>6862964</v>
+        <v>6863070</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747292</v>
+        <v>122747289</v>
       </c>
       <c r="B10" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,34 +1539,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Juvikberget NÖ, Hjd</t>
+          <t>Juvikberget SÖ, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473850</v>
+        <v>473867</v>
       </c>
       <c r="R10" t="n">
-        <v>6862934</v>
+        <v>6862964</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122747288</v>
+        <v>122747292</v>
       </c>
       <c r="B11" t="n">
-        <v>98365</v>
+        <v>79848</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,38 +1641,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Juvikberget Ö, Hjd</t>
+          <t>Juvikberget NÖ, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473875</v>
+        <v>473850</v>
       </c>
       <c r="R11" t="n">
-        <v>6863006</v>
+        <v>6862934</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 60213-2019 artfynd.xlsx
+++ b/artfynd/A 60213-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747288</v>
+        <v>122747252</v>
       </c>
       <c r="B2" t="n">
-        <v>98365</v>
+        <v>79848</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Juvikberget Ö, Hjd</t>
+          <t>Krankpunsen V, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473875</v>
+        <v>473691</v>
       </c>
       <c r="R2" t="n">
-        <v>6863006</v>
+        <v>6863000</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747285</v>
+        <v>122747293</v>
       </c>
       <c r="B3" t="n">
-        <v>90952</v>
+        <v>79848</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,34 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Solandsberget N, Hjd</t>
+          <t>Juvikberget N, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473856</v>
+        <v>473861</v>
       </c>
       <c r="R3" t="n">
-        <v>6863073</v>
+        <v>6862933</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747291</v>
+        <v>122747285</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>90952</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,34 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Juvikberget NÖ, Hjd</t>
+          <t>Solandsberget N, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473850</v>
+        <v>473856</v>
       </c>
       <c r="R4" t="n">
-        <v>6862934</v>
+        <v>6863073</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747293</v>
+        <v>122747291</v>
       </c>
       <c r="B5" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,34 +1009,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Juvikberget N, Hjd</t>
+          <t>Juvikberget NÖ, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473861</v>
+        <v>473850</v>
       </c>
       <c r="R5" t="n">
-        <v>6862933</v>
+        <v>6862934</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747252</v>
+        <v>122747290</v>
       </c>
       <c r="B6" t="n">
-        <v>79848</v>
+        <v>90972</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,34 +1115,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Krankpunsen V, Hjd</t>
+          <t>Juvikberget NÖ, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473691</v>
+        <v>473862</v>
       </c>
       <c r="R6" t="n">
-        <v>6863000</v>
+        <v>6862948</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747290</v>
+        <v>122747288</v>
       </c>
       <c r="B7" t="n">
-        <v>90972</v>
+        <v>98365</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,38 +1217,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Juvikberget NÖ, Hjd</t>
+          <t>Juvikberget Ö, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473862</v>
+        <v>473875</v>
       </c>
       <c r="R7" t="n">
-        <v>6862948</v>
+        <v>6863006</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122747253</v>
+        <v>122747286</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>78150</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,34 +1327,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6437</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Krankpunsen V, Hjd</t>
+          <t>Solandsberget N, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473668</v>
+        <v>473862</v>
       </c>
       <c r="R8" t="n">
-        <v>6863018</v>
+        <v>6863070</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747286</v>
+        <v>122747292</v>
       </c>
       <c r="B9" t="n">
-        <v>78150</v>
+        <v>79848</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,34 +1433,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6437</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Solandsberget N, Hjd</t>
+          <t>Juvikberget NÖ, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473862</v>
+        <v>473850</v>
       </c>
       <c r="R9" t="n">
-        <v>6863070</v>
+        <v>6862934</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,7 +1523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747289</v>
+        <v>122747253</v>
       </c>
       <c r="B10" t="n">
         <v>79847</v>
@@ -1559,14 +1559,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Juvikberget SÖ, Hjd</t>
+          <t>Krankpunsen V, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473867</v>
+        <v>473668</v>
       </c>
       <c r="R10" t="n">
-        <v>6862964</v>
+        <v>6863018</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122747292</v>
+        <v>122747289</v>
       </c>
       <c r="B11" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,34 +1645,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Juvikberget NÖ, Hjd</t>
+          <t>Juvikberget SÖ, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473850</v>
+        <v>473867</v>
       </c>
       <c r="R11" t="n">
-        <v>6862934</v>
+        <v>6862964</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 60213-2019 artfynd.xlsx
+++ b/artfynd/A 60213-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747252</v>
+        <v>122747285</v>
       </c>
       <c r="B2" t="n">
-        <v>79848</v>
+        <v>90952</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Krankpunsen V, Hjd</t>
+          <t>Solandsberget N, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473691</v>
+        <v>473856</v>
       </c>
       <c r="R2" t="n">
-        <v>6863000</v>
+        <v>6863073</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747293</v>
+        <v>122747289</v>
       </c>
       <c r="B3" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,34 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Juvikberget N, Hjd</t>
+          <t>Juvikberget SÖ, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473861</v>
+        <v>473867</v>
       </c>
       <c r="R3" t="n">
-        <v>6862933</v>
+        <v>6862964</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747285</v>
+        <v>122747290</v>
       </c>
       <c r="B4" t="n">
-        <v>90952</v>
+        <v>90972</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,34 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Solandsberget N, Hjd</t>
+          <t>Juvikberget NÖ, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473856</v>
+        <v>473862</v>
       </c>
       <c r="R4" t="n">
-        <v>6863073</v>
+        <v>6862948</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747291</v>
+        <v>122747253</v>
       </c>
       <c r="B5" t="n">
         <v>79847</v>
@@ -1029,14 +1029,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Juvikberget NÖ, Hjd</t>
+          <t>Krankpunsen V, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473850</v>
+        <v>473668</v>
       </c>
       <c r="R5" t="n">
-        <v>6862934</v>
+        <v>6863018</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747290</v>
+        <v>122747293</v>
       </c>
       <c r="B6" t="n">
-        <v>90972</v>
+        <v>79848</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,34 +1115,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Juvikberget NÖ, Hjd</t>
+          <t>Juvikberget N, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473862</v>
+        <v>473861</v>
       </c>
       <c r="R6" t="n">
-        <v>6862948</v>
+        <v>6862933</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747288</v>
+        <v>122747252</v>
       </c>
       <c r="B7" t="n">
-        <v>98365</v>
+        <v>79848</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,38 +1217,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Juvikberget Ö, Hjd</t>
+          <t>Krankpunsen V, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473875</v>
+        <v>473691</v>
       </c>
       <c r="R7" t="n">
-        <v>6863006</v>
+        <v>6863000</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122747286</v>
+        <v>122747292</v>
       </c>
       <c r="B8" t="n">
-        <v>78150</v>
+        <v>79848</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,34 +1327,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6437</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Solandsberget N, Hjd</t>
+          <t>Juvikberget NÖ, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473862</v>
+        <v>473850</v>
       </c>
       <c r="R8" t="n">
-        <v>6863070</v>
+        <v>6862934</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747292</v>
+        <v>122747286</v>
       </c>
       <c r="B9" t="n">
-        <v>79848</v>
+        <v>78150</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,34 +1433,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6437</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Juvikberget NÖ, Hjd</t>
+          <t>Solandsberget N, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473850</v>
+        <v>473862</v>
       </c>
       <c r="R9" t="n">
-        <v>6862934</v>
+        <v>6863070</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747253</v>
+        <v>122747288</v>
       </c>
       <c r="B10" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,38 +1535,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Krankpunsen V, Hjd</t>
+          <t>Juvikberget Ö, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473668</v>
+        <v>473875</v>
       </c>
       <c r="R10" t="n">
-        <v>6863018</v>
+        <v>6863006</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,7 +1629,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122747289</v>
+        <v>122747291</v>
       </c>
       <c r="B11" t="n">
         <v>79847</v>
@@ -1665,14 +1665,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Juvikberget SÖ, Hjd</t>
+          <t>Juvikberget NÖ, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473867</v>
+        <v>473850</v>
       </c>
       <c r="R11" t="n">
-        <v>6862964</v>
+        <v>6862934</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 60213-2019 artfynd.xlsx
+++ b/artfynd/A 60213-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122747285</v>
       </c>
       <c r="B2" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747289</v>
+        <v>122747288</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>98368</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Juvikberget SÖ, Hjd</t>
+          <t>Juvikberget Ö, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473867</v>
+        <v>473875</v>
       </c>
       <c r="R3" t="n">
-        <v>6862964</v>
+        <v>6863006</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747290</v>
+        <v>122747291</v>
       </c>
       <c r="B4" t="n">
-        <v>90972</v>
+        <v>79850</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473862</v>
+        <v>473850</v>
       </c>
       <c r="R4" t="n">
-        <v>6862948</v>
+        <v>6862934</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747253</v>
+        <v>122747252</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>79851</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473668</v>
+        <v>473691</v>
       </c>
       <c r="R5" t="n">
-        <v>6863018</v>
+        <v>6863000</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747293</v>
+        <v>122747292</v>
       </c>
       <c r="B6" t="n">
-        <v>79848</v>
+        <v>79851</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,14 +1135,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Juvikberget N, Hjd</t>
+          <t>Juvikberget NÖ, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473861</v>
+        <v>473850</v>
       </c>
       <c r="R6" t="n">
-        <v>6862933</v>
+        <v>6862934</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747252</v>
+        <v>122747290</v>
       </c>
       <c r="B7" t="n">
-        <v>79848</v>
+        <v>90975</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,34 +1221,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Krankpunsen V, Hjd</t>
+          <t>Juvikberget NÖ, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473691</v>
+        <v>473862</v>
       </c>
       <c r="R7" t="n">
-        <v>6863000</v>
+        <v>6862948</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122747292</v>
+        <v>122747286</v>
       </c>
       <c r="B8" t="n">
-        <v>79848</v>
+        <v>78153</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,34 +1327,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6437</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Juvikberget NÖ, Hjd</t>
+          <t>Solandsberget N, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473850</v>
+        <v>473862</v>
       </c>
       <c r="R8" t="n">
-        <v>6862934</v>
+        <v>6863070</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747286</v>
+        <v>122747293</v>
       </c>
       <c r="B9" t="n">
-        <v>78150</v>
+        <v>79851</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,34 +1433,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6437</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Solandsberget N, Hjd</t>
+          <t>Juvikberget N, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473862</v>
+        <v>473861</v>
       </c>
       <c r="R9" t="n">
-        <v>6863070</v>
+        <v>6862933</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747288</v>
+        <v>122747289</v>
       </c>
       <c r="B10" t="n">
-        <v>98365</v>
+        <v>79850</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,38 +1535,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Juvikberget Ö, Hjd</t>
+          <t>Juvikberget SÖ, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473875</v>
+        <v>473867</v>
       </c>
       <c r="R10" t="n">
-        <v>6863006</v>
+        <v>6862964</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122747291</v>
+        <v>122747253</v>
       </c>
       <c r="B11" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1665,14 +1665,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Juvikberget NÖ, Hjd</t>
+          <t>Krankpunsen V, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473850</v>
+        <v>473668</v>
       </c>
       <c r="R11" t="n">
-        <v>6862934</v>
+        <v>6863018</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 60213-2019 artfynd.xlsx
+++ b/artfynd/A 60213-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122747285</v>
       </c>
       <c r="B2" t="n">
-        <v>90955</v>
+        <v>90957</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helene Andersson, Sanna Strömberg</t>
+          <t>Sanna Strömberg , Helene Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -784,7 +784,7 @@
         <v>122747288</v>
       </c>
       <c r="B3" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747291</v>
+        <v>122747252</v>
       </c>
       <c r="B4" t="n">
-        <v>79850</v>
+        <v>79853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,34 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Juvikberget NÖ, Hjd</t>
+          <t>Krankpunsen V, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473850</v>
+        <v>473691</v>
       </c>
       <c r="R4" t="n">
-        <v>6862934</v>
+        <v>6863000</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747252</v>
+        <v>122747290</v>
       </c>
       <c r="B5" t="n">
-        <v>79851</v>
+        <v>90977</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,34 +1009,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Krankpunsen V, Hjd</t>
+          <t>Juvikberget NÖ, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473691</v>
+        <v>473862</v>
       </c>
       <c r="R5" t="n">
-        <v>6863000</v>
+        <v>6862948</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Helene Andersson, Sanna Strömberg</t>
+          <t>Sanna Strömberg , Helene Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1102,7 +1102,7 @@
         <v>122747292</v>
       </c>
       <c r="B6" t="n">
-        <v>79851</v>
+        <v>79853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Helene Andersson, Sanna Strömberg</t>
+          <t>Sanna Strömberg , Helene Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747290</v>
+        <v>122747286</v>
       </c>
       <c r="B7" t="n">
-        <v>90975</v>
+        <v>78155</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,34 +1221,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>6437</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Juvikberget NÖ, Hjd</t>
+          <t>Solandsberget N, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>473862</v>
       </c>
       <c r="R7" t="n">
-        <v>6862948</v>
+        <v>6863070</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Helene Andersson, Sanna Strömberg</t>
+          <t>Sanna Strömberg , Helene Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122747286</v>
+        <v>122747289</v>
       </c>
       <c r="B8" t="n">
-        <v>78153</v>
+        <v>79852</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,34 +1327,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6437</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Solandsberget N, Hjd</t>
+          <t>Juvikberget SÖ, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473862</v>
+        <v>473867</v>
       </c>
       <c r="R8" t="n">
-        <v>6863070</v>
+        <v>6862964</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Helene Andersson, Sanna Strömberg</t>
+          <t>Sanna Strömberg , Helene Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747293</v>
+        <v>122747291</v>
       </c>
       <c r="B9" t="n">
-        <v>79851</v>
+        <v>79852</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,34 +1433,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Juvikberget N, Hjd</t>
+          <t>Juvikberget NÖ, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473861</v>
+        <v>473850</v>
       </c>
       <c r="R9" t="n">
-        <v>6862933</v>
+        <v>6862934</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Helene Andersson, Sanna Strömberg</t>
+          <t>Sanna Strömberg , Helene Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747289</v>
+        <v>122747253</v>
       </c>
       <c r="B10" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,14 +1559,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Juvikberget SÖ, Hjd</t>
+          <t>Krankpunsen V, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473867</v>
+        <v>473668</v>
       </c>
       <c r="R10" t="n">
-        <v>6862964</v>
+        <v>6863018</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122747253</v>
+        <v>122747293</v>
       </c>
       <c r="B11" t="n">
-        <v>79850</v>
+        <v>79853</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,34 +1645,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Krankpunsen V, Hjd</t>
+          <t>Juvikberget N, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473668</v>
+        <v>473861</v>
       </c>
       <c r="R11" t="n">
-        <v>6863018</v>
+        <v>6862933</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Helene Andersson, Sanna Strömberg</t>
+          <t>Sanna Strömberg , Helene Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
